--- a/uploads/extensiones_teams.xlsx
+++ b/uploads/extensiones_teams.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Call Center\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E9F0F0-84FE-4C93-9C30-C7FC8805AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DEF205-BF59-465E-BD3F-739D28A86525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32115" yWindow="2700" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35025" yWindow="3285" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="alta o baja" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>correo</t>
   </si>
@@ -44,29 +44,32 @@
     <t>código de país + número_alta</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>manfred2@gmail.com</t>
-  </si>
-  <si>
-    <t>manfred1@gmail.com</t>
-  </si>
-  <si>
-    <t>manfred3@gmail.com</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>50640004000</t>
+    <t>memiranda@grupobisa.com</t>
+  </si>
+  <si>
+    <t>avidaurre@grupobisa.com</t>
+  </si>
+  <si>
+    <t>olandivar@grupobisa.com</t>
+  </si>
+  <si>
+    <t>1277</t>
+  </si>
+  <si>
+    <t>1291</t>
+  </si>
+  <si>
+    <t>2268</t>
+  </si>
+  <si>
+    <t>59122317272</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,14 +81,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -138,21 +133,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -479,10 +471,37 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E8" s="2"/>
@@ -495,7 +514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FE848B-5110-40D5-8B94-A2348EA5BBB0}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" style="1" customWidth="1"/>
@@ -519,34 +538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{05E1D2A2-1680-49F4-93F1-58B3405DA782}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{E3B9B06D-FA10-4E61-8CA3-09D11B0CAF0E}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{71A08676-9B5C-45CA-BA6B-762B8A57F4CC}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>